--- a/AAII_Financials/Yearly/GLNG_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/GLNG_YR_FIN.xlsx
@@ -4090,10 +4090,10 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>49300</v>
+        <v>48400</v>
       </c>
       <c r="E83" s="3">
-        <v>53500</v>
+        <v>53000</v>
       </c>
       <c r="F83" s="3">
         <v>50300</v>
